--- a/k7mx9pqw2nl4vb6hr8st/学科HP回収用_分野説明文.xlsx
+++ b/k7mx9pqw2nl4vb6hr8st/学科HP回収用_分野説明文.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sayaka/Dropbox/書類関係/研究室&amp;大学事務/2025.04-2026.03(R7)/広報委員/HP/tmu-sd-cs.github.io/k7mx9pqw2nl4vb6hr8st/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5397FDE6-EC59-7D4A-BC32-B44155835B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A186CA18-0B8E-3B45-B081-6AE1D7E476CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="54640" yWindow="500" windowWidth="25220" windowHeight="24880" xr2:uid="{C027AE32-C706-A545-9D36-AEC2E5152E20}"/>
+    <workbookView xWindow="51380" yWindow="500" windowWidth="27200" windowHeight="24240" xr2:uid="{C027AE32-C706-A545-9D36-AEC2E5152E20}"/>
   </bookViews>
   <sheets>
     <sheet name="現学科メンバー" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="409">
   <si>
     <t>学科HP改修用</t>
     <rPh sb="0" eb="2">
@@ -306,9 +306,6 @@
     <t>I am working on time-frequency analysis, which analyzes temporal variations and periodicity in signals simultaneously to reveal the characteristics and structures of non-stationary signals including acoustic signals. I am also studying binaural technology aiming to reproduce three-dimensional sound field through headphones, which is based on head-related transfer functions including the effects of the head and auricle on sound arriving at the eardrums.</t>
   </si>
   <si>
-    <t>信号処理には、微分積分や線形代数などを基礎としたより高度な数学が背景にあります。今まで学んだ数学を、研究のための武器として使えるようになって欲しいと思います。</t>
-  </si>
-  <si>
     <t>https://researchmap.jp/Tsubasa_Kusano</t>
   </si>
   <si>
@@ -818,13 +815,7 @@
     <t>VLSIs (Integrated Circuits)/Design &amp; Test/Highly Reliable Systems/Dependable Computing</t>
   </si>
   <si>
-    <t>情報システムにおいてはVLSI（大規模集積回路）は重要な部品です．安定なシステムを構築するにはVLSIが正しく動作することを保証しなければなりません．本研究室では主にVLSIの設計とテスト，ディジタルシステムの高信頼化・耐故障性，およびこれらに関連した内容の研究を行っています．</t>
-  </si>
-  <si>
     <t>VLSIs (large-scale integrated circuits) are important components in information systems. To build a stable system, we must ensure that VLSI operates correctly. Our laboratory primarily conducts research into VLSI design and testing, improving the reliability and fault tolerance of digital systems, and related topics.</t>
-  </si>
-  <si>
-    <t>ゲーム機器・家電からロケット・衛に至るまで、様々な機器やシステムにおいてVLSI(大規模集積回路)は重要な部品です。これらを安心して使用するためにはVLSIが正しく動作することを保証しなければなりません。本研究室ではVLSIや情報システムの高信頼化・耐故障性(ディペンダビリティ)やこれらに関連した技術開発の研究を行っています。ユーザが安心して使えるスマートで安全な情報システムの実現を一緒に目指しましょう。</t>
   </si>
   <si>
     <t>渋谷 正弘</t>
@@ -1517,6 +1508,24 @@
   </si>
   <si>
     <t>Yukihisa Suzuki</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>情報システムにおいてはVLSI（集積回路）は重要な部品です．安定なシステムを構築するにはVLSIが正しく動作することを保証しなければなりません．本研究室では主にVLSIの設計とテスト，ディジタルシステムの高信頼化・耐故障性，およびこれらに関連した内容の研究を行っています．</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ゲーム機器・家電からロケット・衛星に至るまで、様々な機器やシステムにおいてVLSI(集積回路)は重要な部品です。これらを安心して使用するためにはVLSIが正しく動作することを保証しなければなりません。本研究室ではVLSIや情報システムの高信頼化・耐故障性(ディペンダビリティ)やこれらに関連した技術開発の研究を行っています。ユーザが安心して使えるスマートで安全な情報システムの実現を一緒に目指しましょう。</t>
+    <rPh sb="16" eb="17">
+      <t xml:space="preserve">ホシ </t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>皆さんの身の回りにある音は、単一の周波数が続く単純なものではなく、いろいろな周波数の音が重なっていたり時間的に複雑に変化したりしています。そのような複雑な信号の構造を明らかにするために、微分積分や複素数、線形代数などを基礎としてより高度な数学を扱います。これまで理解するために勉強してきた数学を、研究のための武器として使いこなせるようになって欲しいと思います。</t>
+  </si>
+  <si>
+    <t>ソーシャル・ネットワーキング・サービスにおけるユーザ間のつながりや、研究者の出版・引用関係など、膨大な社会的・学術的データを対象に、数理モデルやAI技術を駆使して解析を行っています。ネットワーク科学や機械学習などの手法を組み合わせることで、社会的つながりや知識生産の形成・発展メカニズムを定量的に明らかにし、人間社会や学術コミュニティの構造的・動態的特性を理解することを目指しています。</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2052,13 +2061,13 @@
     </row>
     <row r="2" spans="1:12" ht="21">
       <c r="A2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>2</v>
@@ -2104,13 +2113,13 @@
     </row>
     <row r="4" spans="1:12" ht="143.25" customHeight="1">
       <c r="A4" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>13</v>
@@ -2142,13 +2151,13 @@
     </row>
     <row r="5" spans="1:12" ht="126">
       <c r="A5" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>22</v>
@@ -2171,13 +2180,13 @@
     </row>
     <row r="6" spans="1:12" ht="113.25" customHeight="1">
       <c r="A6" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>28</v>
@@ -2206,13 +2215,13 @@
     </row>
     <row r="7" spans="1:12" ht="147">
       <c r="A7" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>36</v>
@@ -2238,13 +2247,13 @@
     </row>
     <row r="8" spans="1:12" ht="126">
       <c r="A8" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>43</v>
@@ -2270,13 +2279,13 @@
     </row>
     <row r="9" spans="1:12" ht="100.5" customHeight="1">
       <c r="A9" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>49</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>50</v>
@@ -2305,13 +2314,13 @@
     </row>
     <row r="10" spans="1:12" ht="126">
       <c r="A10" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>56</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>57</v>
@@ -2326,45 +2335,45 @@
         <v>60</v>
       </c>
       <c r="H10" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="I10" s="13" t="s">
         <v>61</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>62</v>
       </c>
       <c r="K10" s="7" t="b">
         <v>1</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="84">
       <c r="A11" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="D11" s="8" t="s">
+      <c r="E11" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="F11" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="G11" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="H11" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="I11" s="13" t="s">
         <v>69</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>70</v>
       </c>
       <c r="J11" s="14" t="s">
         <v>34</v>
@@ -2373,12 +2382,12 @@
         <v>1</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="1" customFormat="1">
       <c r="B12" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="9">
@@ -2392,69 +2401,69 @@
     </row>
     <row r="13" spans="1:12" ht="166.5" customHeight="1">
       <c r="A13" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="D13" s="8" t="s">
+      <c r="E13" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="F13" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="G13" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="H13" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="I13" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="I13" s="13" t="s">
+      <c r="J13" s="14" t="s">
         <v>79</v>
-      </c>
-      <c r="J13" s="14" t="s">
-        <v>80</v>
       </c>
       <c r="K13" s="7" t="b">
         <v>1</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="147">
       <c r="A14" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="D14" s="8" t="s">
+      <c r="E14" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="F14" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="G14" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="H14" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="J14" s="14" t="s">
         <v>87</v>
-      </c>
-      <c r="J14" s="14" t="s">
-        <v>88</v>
       </c>
       <c r="K14" s="7" t="b">
         <v>0</v>
@@ -2462,34 +2471,34 @@
     </row>
     <row r="15" spans="1:12" ht="189">
       <c r="A15" t="s">
+        <v>383</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="D15" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="D15" s="8" t="s">
+      <c r="E15" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="F15" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="G15" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="H15" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="I15" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="I15" s="13" t="s">
+      <c r="J15" s="14" t="s">
         <v>97</v>
-      </c>
-      <c r="J15" s="14" t="s">
-        <v>98</v>
       </c>
       <c r="K15" s="7" t="b">
         <v>0</v>
@@ -2497,31 +2506,31 @@
     </row>
     <row r="16" spans="1:12" ht="111.75" customHeight="1">
       <c r="A16" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="D16" s="8" t="s">
+      <c r="E16" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="F16" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="G16" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="H16" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="J16" s="14" t="s">
         <v>104</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>105</v>
       </c>
       <c r="K16" s="7" t="b">
         <v>1</v>
@@ -2529,28 +2538,28 @@
     </row>
     <row r="17" spans="1:12" ht="57" customHeight="1">
       <c r="A17" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="D17" s="8" t="s">
+      <c r="E17" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="F17" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="H17" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="J17" s="13" t="s">
         <v>110</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>111</v>
       </c>
       <c r="K17" s="7" t="b">
         <v>0</v>
@@ -2558,42 +2567,42 @@
     </row>
     <row r="18" spans="1:12" ht="126">
       <c r="A18" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="D18" s="8" t="s">
+      <c r="E18" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="F18" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="G18" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="H18" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="I18" s="13" t="s">
         <v>117</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>118</v>
       </c>
       <c r="K18" s="7" t="b">
         <v>1</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="1" customFormat="1">
       <c r="B19" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="9">
@@ -2607,72 +2616,72 @@
     </row>
     <row r="20" spans="1:12" ht="138" customHeight="1">
       <c r="A20" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="D20" s="8" t="s">
+      <c r="E20" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="F20" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="G20" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="H20" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="I20" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I20" s="12" t="s">
+      <c r="J20" s="13" t="s">
         <v>127</v>
-      </c>
-      <c r="J20" s="13" t="s">
-        <v>128</v>
       </c>
       <c r="K20" s="7" t="b">
         <v>1</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="189">
       <c r="A21" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="D21" s="8" t="s">
+      <c r="E21" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="F21" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="G21" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="H21" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="I21" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="I21" s="13" t="s">
+      <c r="J21" s="14" t="s">
         <v>136</v>
-      </c>
-      <c r="J21" s="14" t="s">
-        <v>137</v>
       </c>
       <c r="K21" s="7" t="b">
         <v>0</v>
@@ -2680,34 +2689,34 @@
     </row>
     <row r="22" spans="1:12" ht="168">
       <c r="A22" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="D22" s="8" t="s">
+      <c r="E22" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="F22" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="G22" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="H22" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="I22" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="I22" s="13" t="s">
+      <c r="J22" s="14" t="s">
         <v>144</v>
-      </c>
-      <c r="J22" s="14" t="s">
-        <v>145</v>
       </c>
       <c r="K22" s="7" t="b">
         <v>0</v>
@@ -2715,31 +2724,31 @@
     </row>
     <row r="23" spans="1:12" ht="84">
       <c r="A23" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="D23" s="8" t="s">
+      <c r="E23" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="F23" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="G23" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="H23" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="I23" s="13" t="s">
         <v>151</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>152</v>
       </c>
       <c r="K23" s="7" t="b">
         <v>0</v>
@@ -2747,66 +2756,66 @@
     </row>
     <row r="24" spans="1:12" ht="168">
       <c r="A24" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="D24" s="8" t="s">
+      <c r="E24" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="E24" s="8" t="s">
-        <v>155</v>
-      </c>
       <c r="F24" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="G24" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="H24" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="I24" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="J24" s="14" t="s">
         <v>159</v>
-      </c>
-      <c r="J24" s="14" t="s">
-        <v>160</v>
       </c>
       <c r="K24" s="7" t="b">
         <v>1</v>
       </c>
       <c r="L24" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="189">
       <c r="A25" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="D25" s="8" t="s">
+      <c r="E25" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="F25" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="G25" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="H25" s="8" t="s">
         <v>166</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>167</v>
       </c>
       <c r="K25" s="7" t="b">
         <v>0</v>
@@ -2814,7 +2823,7 @@
     </row>
     <row r="26" spans="1:12" s="1" customFormat="1">
       <c r="B26" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="9">
@@ -2828,34 +2837,34 @@
     </row>
     <row r="27" spans="1:12" ht="139.5" customHeight="1">
       <c r="A27" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="D27" s="8" t="s">
+      <c r="E27" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="F27" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="G27" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="H27" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="I27" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="J27" s="8" t="s">
         <v>175</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>176</v>
       </c>
       <c r="K27" s="7" t="b">
         <v>0</v>
@@ -2863,28 +2872,28 @@
     </row>
     <row r="28" spans="1:12" ht="114" customHeight="1">
       <c r="A28" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="D28" s="8" t="s">
+      <c r="E28" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="F28" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="G28" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="H28" s="8" t="s">
         <v>181</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>182</v>
       </c>
       <c r="K28" s="7" t="b">
         <v>0</v>
@@ -2892,34 +2901,34 @@
     </row>
     <row r="29" spans="1:12" ht="189">
       <c r="A29" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="D29" s="8" t="s">
+      <c r="E29" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="F29" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="G29" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="H29" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="H29" s="8" t="s">
+      <c r="I29" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="I29" s="11" t="s">
+      <c r="J29" s="8" t="s">
         <v>189</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>190</v>
       </c>
       <c r="K29" s="7" t="b">
         <v>1</v>
@@ -2928,34 +2937,34 @@
     </row>
     <row r="30" spans="1:12" ht="199.5" customHeight="1">
       <c r="A30" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="D30" s="8" t="s">
+      <c r="E30" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="F30" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="G30" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="G30" s="8" t="s">
+      <c r="H30" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="H30" s="8" t="s">
+      <c r="I30" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="I30" s="13" t="s">
+      <c r="J30" s="14" t="s">
         <v>197</v>
-      </c>
-      <c r="J30" s="14" t="s">
-        <v>198</v>
       </c>
       <c r="K30" s="7" t="b">
         <v>0</v>
@@ -2963,19 +2972,19 @@
     </row>
     <row r="31" spans="1:12" ht="93" customHeight="1">
       <c r="A31" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I31" s="13"/>
       <c r="J31" s="14"/>
@@ -2985,34 +2994,34 @@
     </row>
     <row r="32" spans="1:12" ht="94.5" customHeight="1">
       <c r="A32" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E32" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F32" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="G32" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="H32" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="H32" s="8" t="s">
+      <c r="I32" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="I32" s="13" t="s">
-        <v>205</v>
-      </c>
       <c r="J32" s="14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K32" s="7" t="b">
         <v>0</v>
@@ -3020,7 +3029,7 @@
     </row>
     <row r="33" spans="1:12" s="1" customFormat="1">
       <c r="B33" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="9">
@@ -3034,66 +3043,66 @@
     </row>
     <row r="34" spans="1:12" ht="210">
       <c r="A34" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="H34" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="I34" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="I34" s="13" t="s">
+      <c r="J34" s="13" t="s">
         <v>210</v>
-      </c>
-      <c r="J34" s="13" t="s">
-        <v>211</v>
       </c>
       <c r="K34" s="7" t="b">
         <v>0</v>
       </c>
       <c r="L34" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="189">
       <c r="A35" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="D35" s="8" t="s">
+      <c r="E35" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="F35" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="G35" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="G35" s="8" t="s">
+      <c r="H35" s="8" t="s">
         <v>217</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>218</v>
       </c>
       <c r="I35" s="8" t="s">
         <v>55</v>
@@ -3105,33 +3114,33 @@
         <v>0</v>
       </c>
       <c r="L35" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="84">
       <c r="A36" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="D36" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="C36" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="D36" s="8" t="s">
+      <c r="E36" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="F36" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="G36" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="F36" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>223</v>
-      </c>
       <c r="H36" s="8" t="s">
-        <v>224</v>
+        <v>406</v>
       </c>
       <c r="I36" s="8" t="s">
         <v>55</v>
@@ -3145,28 +3154,28 @@
     </row>
     <row r="37" spans="1:12" ht="105">
       <c r="A37" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="F37" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="D37" s="8" t="s">
+      <c r="G37" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="H37" s="8" t="s">
         <v>227</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>230</v>
       </c>
       <c r="K37" s="7" t="b">
         <v>0</v>
@@ -3174,66 +3183,66 @@
     </row>
     <row r="38" spans="1:12" ht="125.25" customHeight="1">
       <c r="A38" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="F38" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="D38" s="8" t="s">
+      <c r="G38" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="H38" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="F38" s="8" t="s">
+      <c r="I38" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="G38" s="8" t="s">
+      <c r="J38" s="14" t="s">
         <v>235</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="I38" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="J38" s="14" t="s">
-        <v>238</v>
       </c>
       <c r="K38" s="7" t="b">
         <v>0</v>
       </c>
       <c r="L38" s="13" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="84">
       <c r="A39" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="F39" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="D39" s="8" t="s">
+      <c r="G39" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="H39" s="8" t="s">
         <v>242</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="H39" s="8" t="s">
-        <v>245</v>
       </c>
       <c r="K39" s="7" t="b">
         <v>0</v>
@@ -3241,19 +3250,19 @@
     </row>
     <row r="40" spans="1:12" ht="42">
       <c r="A40" t="s">
+        <v>390</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="D40" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="H40" s="8" t="s">
         <v>394</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>397</v>
       </c>
       <c r="K40" s="7" t="b">
         <v>0</v>
@@ -3261,7 +3270,7 @@
     </row>
     <row r="41" spans="1:12" s="1" customFormat="1">
       <c r="B41" s="3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="9">
@@ -3275,45 +3284,45 @@
     </row>
     <row r="42" spans="1:12" ht="147">
       <c r="B42" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="F42" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="D42" s="12" t="s">
+      <c r="G42" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="E42" s="12" t="s">
+      <c r="H42" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="F42" s="12" t="s">
+      <c r="I42" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="G42" s="12" t="s">
+      <c r="J42" s="14" t="s">
         <v>251</v>
-      </c>
-      <c r="H42" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="I42" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="J42" s="14" t="s">
-        <v>254</v>
       </c>
       <c r="K42" s="7" t="b">
         <v>1</v>
       </c>
       <c r="L42" s="13" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="B43" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="K43" s="7" t="b">
         <v>0</v>
@@ -3321,7 +3330,7 @@
     </row>
     <row r="44" spans="1:12" s="1" customFormat="1">
       <c r="B44" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="9">
@@ -3335,28 +3344,28 @@
     </row>
     <row r="45" spans="1:12" ht="168">
       <c r="A45" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="F45" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="C45" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="D45" s="8" t="s">
+      <c r="G45" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="H45" s="8" t="s">
         <v>260</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="H45" s="8" t="s">
-        <v>263</v>
       </c>
       <c r="K45" s="7" t="b">
         <v>0</v>
@@ -3364,34 +3373,34 @@
     </row>
     <row r="46" spans="1:12" ht="147" customHeight="1">
       <c r="A46" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="F46" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="C46" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="D46" s="8" t="s">
+      <c r="G46" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="H46" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="I46" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="G46" s="8" t="s">
+      <c r="J46" s="14" t="s">
         <v>268</v>
-      </c>
-      <c r="H46" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="I46" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="J46" s="14" t="s">
-        <v>271</v>
       </c>
       <c r="K46" s="7" t="b">
         <v>0</v>
@@ -3473,13 +3482,13 @@
     </row>
     <row r="2" spans="1:12" ht="21">
       <c r="A2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>2</v>
@@ -3511,7 +3520,7 @@
     </row>
     <row r="3" spans="1:12" s="1" customFormat="1">
       <c r="B3" s="3" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C3" s="3">
         <v>4</v>
@@ -3525,13 +3534,13 @@
     </row>
     <row r="4" spans="1:12" ht="126">
       <c r="A4" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>22</v>
@@ -3554,13 +3563,13 @@
     </row>
     <row r="5" spans="1:12" ht="113.25" customHeight="1">
       <c r="A5" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>28</v>
@@ -3589,13 +3598,13 @@
     </row>
     <row r="6" spans="1:12" ht="126">
       <c r="A6" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>43</v>
@@ -3621,31 +3630,31 @@
     </row>
     <row r="7" spans="1:12" ht="84">
       <c r="A7" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="E7" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="F7" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="G7" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="H7" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="I7" s="13" t="s">
         <v>69</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>70</v>
       </c>
       <c r="J7" s="14" t="s">
         <v>34</v>
@@ -3654,12 +3663,12 @@
         <v>1</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="1" customFormat="1">
       <c r="B8" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C8" s="5">
         <v>5</v>
@@ -3673,69 +3682,69 @@
     </row>
     <row r="9" spans="1:12" ht="166.5" customHeight="1">
       <c r="A9" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="E9" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="F9" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="G9" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="H9" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="I9" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="J9" s="14" t="s">
         <v>79</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>80</v>
       </c>
       <c r="K9" s="7" t="b">
         <v>1</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="147">
       <c r="A10" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="D10" s="8" t="s">
+      <c r="E10" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="F10" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="G10" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="H10" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="J10" s="14" t="s">
         <v>87</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>88</v>
       </c>
       <c r="K10" s="7" t="b">
         <v>0</v>
@@ -3743,34 +3752,34 @@
     </row>
     <row r="11" spans="1:12" ht="189">
       <c r="A11" t="s">
+        <v>383</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="D11" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="D11" s="8" t="s">
+      <c r="E11" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="F11" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="G11" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="H11" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="I11" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="J11" s="14" t="s">
         <v>97</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>98</v>
       </c>
       <c r="K11" s="7" t="b">
         <v>0</v>
@@ -3778,31 +3787,31 @@
     </row>
     <row r="12" spans="1:12" ht="111.75" customHeight="1">
       <c r="A12" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="D12" s="8" t="s">
+      <c r="E12" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="F12" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="G12" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="H12" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="J12" s="14" t="s">
         <v>104</v>
-      </c>
-      <c r="J12" s="14" t="s">
-        <v>105</v>
       </c>
       <c r="K12" s="7" t="b">
         <v>1</v>
@@ -3810,42 +3819,42 @@
     </row>
     <row r="13" spans="1:12" ht="126">
       <c r="A13" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="D13" s="8" t="s">
+      <c r="E13" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="F13" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="G13" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="H13" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="I13" s="13" t="s">
         <v>117</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>118</v>
       </c>
       <c r="K13" s="7" t="b">
         <v>1</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="1" customFormat="1">
       <c r="B14" s="3" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C14" s="3">
         <v>9</v>
@@ -3859,72 +3868,72 @@
     </row>
     <row r="15" spans="1:12" ht="138" customHeight="1">
       <c r="A15" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="D15" s="8" t="s">
+      <c r="E15" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="F15" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="G15" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="H15" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="I15" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="J15" s="13" t="s">
         <v>127</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>128</v>
       </c>
       <c r="K15" s="7" t="b">
         <v>1</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="168">
       <c r="A16" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="D16" s="8" t="s">
+      <c r="E16" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="F16" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="G16" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="H16" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="I16" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="I16" s="13" t="s">
+      <c r="J16" s="14" t="s">
         <v>144</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>145</v>
       </c>
       <c r="K16" s="7" t="b">
         <v>0</v>
@@ -3932,34 +3941,34 @@
     </row>
     <row r="17" spans="1:12" ht="139.5" customHeight="1">
       <c r="A17" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="D17" s="8" t="s">
+      <c r="E17" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="F17" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="G17" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="H17" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="I17" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="J17" s="8" t="s">
         <v>175</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>176</v>
       </c>
       <c r="K17" s="7" t="b">
         <v>0</v>
@@ -3967,34 +3976,34 @@
     </row>
     <row r="18" spans="1:12" ht="189">
       <c r="A18" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="D18" s="8" t="s">
+      <c r="E18" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="F18" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="G18" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="H18" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="I18" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="I18" s="11" t="s">
+      <c r="J18" s="8" t="s">
         <v>189</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>190</v>
       </c>
       <c r="K18" s="7" t="b">
         <v>1</v>
@@ -4003,34 +4012,34 @@
     </row>
     <row r="19" spans="1:12" ht="199.5" customHeight="1">
       <c r="A19" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="D19" s="8" t="s">
+      <c r="E19" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="F19" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="G19" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="H19" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="I19" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="I19" s="13" t="s">
+      <c r="J19" s="14" t="s">
         <v>197</v>
-      </c>
-      <c r="J19" s="14" t="s">
-        <v>198</v>
       </c>
       <c r="K19" s="7" t="b">
         <v>0</v>
@@ -4038,19 +4047,19 @@
     </row>
     <row r="20" spans="1:12" ht="93" customHeight="1">
       <c r="A20" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I20" s="13"/>
       <c r="J20" s="14"/>
@@ -4060,72 +4069,72 @@
     </row>
     <row r="21" spans="1:12" ht="168">
       <c r="A21" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="D21" s="8" t="s">
+      <c r="E21" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="F21" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="G21" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="H21" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="I21" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="J21" s="14" t="s">
         <v>159</v>
-      </c>
-      <c r="J21" s="14" t="s">
-        <v>160</v>
       </c>
       <c r="K21" s="7" t="b">
         <v>1</v>
       </c>
       <c r="L21" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="94.5" customHeight="1">
       <c r="A22" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="D22" s="8" t="s">
+      <c r="E22" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="F22" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="G22" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="H22" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="I22" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="I22" s="13" t="s">
-        <v>205</v>
-      </c>
       <c r="J22" s="14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K22" s="7" t="b">
         <v>0</v>
@@ -4133,28 +4142,28 @@
     </row>
     <row r="23" spans="1:12" ht="189">
       <c r="A23" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="D23" s="8" t="s">
+      <c r="E23" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="F23" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="G23" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="H23" s="8" t="s">
         <v>166</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>167</v>
       </c>
       <c r="K23" s="7" t="b">
         <v>0</v>
@@ -4162,7 +4171,7 @@
     </row>
     <row r="24" spans="1:12" s="1" customFormat="1">
       <c r="B24" s="3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="9">
@@ -4176,45 +4185,45 @@
     </row>
     <row r="25" spans="1:12" ht="147">
       <c r="B25" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="F25" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="D25" s="12" t="s">
+      <c r="G25" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="H25" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="I25" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="G25" s="12" t="s">
+      <c r="J25" s="14" t="s">
         <v>251</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="I25" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="J25" s="14" t="s">
-        <v>254</v>
       </c>
       <c r="K25" s="7" t="b">
         <v>1</v>
       </c>
       <c r="L25" s="13" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="B26" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D26" s="12"/>
       <c r="K26" s="7" t="b">
@@ -4223,7 +4232,7 @@
     </row>
     <row r="27" spans="1:12" s="1" customFormat="1">
       <c r="B27" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="9">
@@ -4237,28 +4246,28 @@
     </row>
     <row r="28" spans="1:12" ht="168">
       <c r="A28" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="F28" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="D28" s="8" t="s">
+      <c r="G28" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="H28" s="8" t="s">
         <v>260</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>263</v>
       </c>
       <c r="K28" s="7" t="b">
         <v>0</v>
@@ -4266,34 +4275,34 @@
     </row>
     <row r="29" spans="1:12" ht="147" customHeight="1">
       <c r="A29" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="F29" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="D29" s="8" t="s">
+      <c r="G29" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="H29" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="I29" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="J29" s="14" t="s">
         <v>268</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="J29" s="14" t="s">
-        <v>271</v>
       </c>
       <c r="K29" s="7" t="b">
         <v>0</v>
@@ -4368,41 +4377,41 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21">
       <c r="A1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>272</v>
-      </c>
-      <c r="B1" t="s">
-        <v>273</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="84">
       <c r="A2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B2" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="84">
       <c r="A3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B3" t="s">
         <v>276</v>
       </c>
-      <c r="B3" t="s">
-        <v>279</v>
-      </c>
       <c r="C3" s="8" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>26</v>
@@ -4410,24 +4419,24 @@
     </row>
     <row r="4" spans="1:5" ht="84">
       <c r="A4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="84">
       <c r="A5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>36</v>
@@ -4438,13 +4447,13 @@
     </row>
     <row r="6" spans="1:5" ht="84">
       <c r="A6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>54</v>
@@ -4452,395 +4461,395 @@
     </row>
     <row r="7" spans="1:5" ht="100" customHeight="1">
       <c r="A7" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B7" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E7" s="8"/>
     </row>
     <row r="8" spans="1:5" ht="42">
       <c r="A8" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B8" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="21">
       <c r="A9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B9" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="84">
       <c r="A10" t="s">
+        <v>292</v>
+      </c>
+      <c r="B10" t="s">
+        <v>293</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>295</v>
-      </c>
-      <c r="B10" t="s">
-        <v>296</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="84">
       <c r="A11" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B11" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="105">
       <c r="A12" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B12" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C12" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>89</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="84">
       <c r="A13" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B13" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="84">
       <c r="A14" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B14" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="42">
       <c r="A15" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B15" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="42">
       <c r="A16" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B16" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="84">
       <c r="A17" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B17" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="84">
       <c r="A18" t="s">
+        <v>312</v>
+      </c>
+      <c r="B18" t="s">
         <v>315</v>
       </c>
-      <c r="B18" t="s">
-        <v>318</v>
-      </c>
       <c r="C18" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="84">
       <c r="A19" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B19" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="63">
       <c r="A20" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B20" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="42">
       <c r="A21" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B21" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="42">
       <c r="A22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B22" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="21">
       <c r="A23" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B23" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="84">
       <c r="A24" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B24" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="84">
       <c r="A25" t="s">
+        <v>327</v>
+      </c>
+      <c r="B25" t="s">
         <v>330</v>
       </c>
-      <c r="B25" t="s">
-        <v>333</v>
-      </c>
       <c r="C25" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="84">
       <c r="A26" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B26" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="84">
       <c r="A27" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B27" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="42">
       <c r="A28" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B28" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="84">
       <c r="A29" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B29" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C29" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>208</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="84">
       <c r="A30" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B30" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="84">
       <c r="A31" t="s">
+        <v>337</v>
+      </c>
+      <c r="B31" t="s">
         <v>340</v>
       </c>
-      <c r="B31" t="s">
-        <v>343</v>
-      </c>
       <c r="C31" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="21">
       <c r="A32" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B32" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="84">
       <c r="A33" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B33" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="42">
       <c r="A34" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B34" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -4851,12 +4860,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="897971a1-34b9-4259-b4e6-957b93aa4e71">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="475beba0-ee97-4a07-a027-60ea5346ed7f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5061,20 +5072,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="897971a1-34b9-4259-b4e6-957b93aa4e71">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="475beba0-ee97-4a07-a027-60ea5346ed7f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A761A6CF-0473-4AE9-9FFD-D107C9271965}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF085B98-31CF-48BE-9DF2-540E3380136C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="897971a1-34b9-4259-b4e6-957b93aa4e71"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="475beba0-ee97-4a07-a027-60ea5346ed7f"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5099,18 +5117,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF085B98-31CF-48BE-9DF2-540E3380136C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A761A6CF-0473-4AE9-9FFD-D107C9271965}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="897971a1-34b9-4259-b4e6-957b93aa4e71"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="475beba0-ee97-4a07-a027-60ea5346ed7f"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>